--- a/ExcelFiles/PatientView.xlsx
+++ b/ExcelFiles/PatientView.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Riomed\Cellma4ClinicalAuto\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0435DBA4-B9A3-4DC8-97BA-90D073766784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5F95B8-2376-4BCE-B1F4-E193249DBFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="-21600" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loginDetails" sheetId="2" r:id="rId1"/>
     <sheet name="PatientDetails" sheetId="3" r:id="rId2"/>
+    <sheet name="PatientViewSections" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="116">
   <si>
     <t>username</t>
   </si>
@@ -274,6 +275,117 @@
   </si>
   <si>
     <t>Female</t>
+  </si>
+  <si>
+    <t>selector</t>
+  </si>
+  <si>
+    <t>popUp</t>
+  </si>
+  <si>
+    <t>Hot food</t>
+  </si>
+  <si>
+    <t>Allergies History</t>
+  </si>
+  <si>
+    <t>Diagnosis History</t>
+  </si>
+  <si>
+    <t>Heart Valve Disorder</t>
+  </si>
+  <si>
+    <t>selector2</t>
+  </si>
+  <si>
+    <t>Cochlear Implantation</t>
+  </si>
+  <si>
+    <t>Dermabrasion</t>
+  </si>
+  <si>
+    <t>Respiratory</t>
+  </si>
+  <si>
+    <t>Brain tumour</t>
+  </si>
+  <si>
+    <t>Aspirin 100mg capsules</t>
+  </si>
+  <si>
+    <t>Cochlear structure</t>
+  </si>
+  <si>
+    <t>Renal Function Test</t>
+  </si>
+  <si>
+    <t>Reproductive finding</t>
+  </si>
+  <si>
+    <t>Alcohol misuse</t>
+  </si>
+  <si>
+    <t>Secondary school education</t>
+  </si>
+  <si>
+    <t>Disorder of lymphatics</t>
+  </si>
+  <si>
+    <t>DAS28</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Dietary advice</t>
+  </si>
+  <si>
+    <t>Pregnancy 1</t>
+  </si>
+  <si>
+    <t>Procedures History</t>
+  </si>
+  <si>
+    <t>Conditions History</t>
+  </si>
+  <si>
+    <t>Medications History</t>
+  </si>
+  <si>
+    <t>Devices History</t>
+  </si>
+  <si>
+    <t>Investigations History</t>
+  </si>
+  <si>
+    <t>Examinations History</t>
+  </si>
+  <si>
+    <t>Lifestyle History</t>
+  </si>
+  <si>
+    <t>Social Circumstances History</t>
+  </si>
+  <si>
+    <t>Risk Factors History</t>
+  </si>
+  <si>
+    <t>Test/Tools History</t>
+  </si>
+  <si>
+    <t>Interpretations History</t>
+  </si>
+  <si>
+    <t>Recommendations History</t>
+  </si>
+  <si>
+    <t>Pregnancies History</t>
+  </si>
+  <si>
+    <t>Current Problems and Symptoms History</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -318,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -334,6 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -962,7 +1075,222 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD60B4E-8110-4DE8-A80C-7125F68639E9}">
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="563c2453-77f6-4899-a3ec-7eb6553b4f66">
@@ -971,15 +1299,6 @@
     <TaxCatchAll xmlns="c9416fa7-6169-4354-a691-3cfdebf72cd6" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1238,20 +1557,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101DBEFA-2EFF-47B2-92EB-3E72B43EE2A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE0B556D-2173-4F7C-9F53-AE9A9D15CB9C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="563c2453-77f6-4899-a3ec-7eb6553b4f66"/>
     <ds:schemaRef ds:uri="c9416fa7-6169-4354-a691-3cfdebf72cd6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101DBEFA-2EFF-47B2-92EB-3E72B43EE2A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
